--- a/Result/profitability/6239.xlsx
+++ b/Result/profitability/6239.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.81</v>
       </c>
       <c r="M2" t="n">
-        <v>2.13875</v>
+        <v>2.22875</v>
       </c>
       <c r="N2" t="n">
-        <v>19.54625</v>
+        <v>19.58625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.98</v>
       </c>
       <c r="M3" t="n">
-        <v>2.22625</v>
+        <v>2.34625</v>
       </c>
       <c r="N3" t="n">
-        <v>20.2825</v>
+        <v>20.71</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -792,7 +792,7 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>2.7</v>
       </c>
       <c r="M4" t="n">
-        <v>2.30875</v>
+        <v>2.48625</v>
       </c>
       <c r="N4" t="n">
-        <v>21.4075</v>
+        <v>21.99625</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>2.57</v>
       </c>
       <c r="M5" t="n">
-        <v>2.4325</v>
+        <v>2.645</v>
       </c>
       <c r="N5" t="n">
-        <v>22.47625</v>
+        <v>23.20625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>2.43375</v>
+        <v>2.54875</v>
       </c>
       <c r="N6" t="n">
-        <v>22.905</v>
+        <v>23.60875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.65</v>
       </c>
       <c r="M7" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="N7" t="n">
-        <v>23.58875</v>
+        <v>23.97875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>2.12</v>
       </c>
       <c r="M8" t="n">
-        <v>2.33</v>
+        <v>2.3925</v>
       </c>
       <c r="N8" t="n">
-        <v>24.45</v>
+        <v>24.74</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6239</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>23116</v>
+      </c>
+      <c r="D75" t="n">
+        <v>18085</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5031</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.76</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3531</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>131</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3661</v>
+      </c>
+      <c r="K75" t="n">
+        <v>2219</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.1625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1193415637860082</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.307692307692307</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.840000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3668341708542715</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
